--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1935,6 +1935,112 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129000426</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78881</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nylandet, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>526867</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6909359</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -1940,7 +1940,7 @@
         <v>129000426</v>
       </c>
       <c r="B13" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -1940,7 +1940,7 @@
         <v>129000426</v>
       </c>
       <c r="B13" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -1940,7 +1940,7 @@
         <v>129000426</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -1940,7 +1940,7 @@
         <v>129000426</v>
       </c>
       <c r="B13" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -1940,7 +1940,7 @@
         <v>129000426</v>
       </c>
       <c r="B13" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -1940,7 +1940,7 @@
         <v>129000426</v>
       </c>
       <c r="B13" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87748116</v>
+        <v>87748243</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526642.149245263</v>
+        <v>526612</v>
       </c>
       <c r="R2" t="n">
-        <v>6909378.674951208</v>
+        <v>6909580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fåtalig</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87748131</v>
+        <v>87748159</v>
       </c>
       <c r="B3" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,43 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>2387</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526667</v>
+        <v>526606</v>
       </c>
       <c r="R3" t="n">
-        <v>6909457</v>
+        <v>6909318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87748159</v>
+        <v>87748272</v>
       </c>
       <c r="B4" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526606.3053464779</v>
+        <v>526571</v>
       </c>
       <c r="R4" t="n">
-        <v>6909318.40612179</v>
+        <v>6909262</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,19 +937,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,55 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87749348</v>
+        <v>87748276</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>526623.767352659</v>
+        <v>526912</v>
       </c>
       <c r="R5" t="n">
-        <v>6909347.83947773</v>
+        <v>6909361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,19 +1034,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87748121</v>
+        <v>129000426</v>
       </c>
       <c r="B6" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1170,21 +1096,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Riberget, Hls</t>
+          <t>Nylandet, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526672.5519161794</v>
+        <v>526867</v>
       </c>
       <c r="R6" t="n">
-        <v>6909478.88805186</v>
+        <v>6909359</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,22 +1132,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,27 +1157,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87748133</v>
+        <v>87748259</v>
       </c>
       <c r="B7" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,43 +1180,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>526648</v>
+        <v>526668</v>
       </c>
       <c r="R7" t="n">
-        <v>6909368</v>
+        <v>6909453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,16 +1269,11 @@
         <v>87747848</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1409,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526623.3607659944</v>
+        <v>526623</v>
       </c>
       <c r="R8" t="n">
-        <v>6909340.39632883</v>
+        <v>6909340</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,19 +1339,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,15 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87748132</v>
+        <v>87747844</v>
       </c>
       <c r="B9" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,31 +1379,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1530,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526620</v>
+        <v>526387</v>
       </c>
       <c r="R9" t="n">
-        <v>6909352</v>
+        <v>6909224</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,12 +1438,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,15 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87748259</v>
+        <v>87749348</v>
       </c>
       <c r="B10" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,34 +1481,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526667.6333980786</v>
+        <v>526624</v>
       </c>
       <c r="R10" t="n">
-        <v>6909453.275128965</v>
+        <v>6909348</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,19 +1543,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,15 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87748115</v>
+        <v>87748109</v>
       </c>
       <c r="B11" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,31 +1583,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1753,10 +1616,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526667.9548354021</v>
+        <v>526814</v>
       </c>
       <c r="R11" t="n">
-        <v>6909471.411860239</v>
+        <v>6909471</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,22 +1646,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,50 +1678,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87748272</v>
+        <v>87748131</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526570.8926537653</v>
+        <v>526667</v>
       </c>
       <c r="R12" t="n">
-        <v>6909262.325093894</v>
+        <v>6909457</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,19 +1755,9 @@
           <t>2020-07-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-07-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,49 +1784,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129000426</v>
+        <v>87748132</v>
       </c>
       <c r="B13" t="n">
-        <v>78801</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nylandet, Hls</t>
+          <t>Riberget, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526867</v>
+        <v>526620</v>
       </c>
       <c r="R13" t="n">
-        <v>6909359</v>
+        <v>6909352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2006,17 +1858,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,15 +1878,745 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>87748133</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>526648</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6909368</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>87748121</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>526673</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6909479</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>94434083</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-Svenskmyrtjärnen, Rödtjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>526574</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6909553</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-08-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>87748082</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>526814</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6909463</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fåtalig</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>87748115</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>526668</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6909471</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>87748116</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>526642</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6909379</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-07-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fåtalig</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>87748068</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>526818</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6909470</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44476-2025 artfynd.xlsx
+++ b/artfynd/A 44476-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748243</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748272</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748276</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000426</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748259</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87747848</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87747844</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87749348</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748109</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748131</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748132</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748133</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748121</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2201,6 +2276,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94434083</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748082</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748115</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748116</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2617,8 +2712,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>